--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Évènement documenté</t>
+    <t>Modèle métier - Évènement documenté</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Évènement (acte, traitement, diagnostic, etc…) décrit dans le document.Il y a au minimum une occurrence de cet élément pour décrire l'évènement principal avec obligatoirement une date de début et un exécutant.</t>
+    <t>Évènement (acte, traitement, diagnostic, etc…) décrit dans le document. Il y a au minimum une occurrence de cet élément pour décrire l'évènement principal avec obligatoirement une date de début et un exécutant.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -234,7 +234,7 @@
     <t/>
   </si>
   <si>
-    <t>0</t>
+    <t>1</t>
   </si>
   <si>
     <t>*</t>
@@ -247,6 +247,9 @@
     <t>Base</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Evenement.identifiantEvenement</t>
   </si>
   <si>
@@ -254,20 +257,27 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l’évènement documenté .</t>
+    <t>Identifiant de l’évènement documenté. 
+ Obligatoire pour :
+  - une demande d'acte d'imagerie pour porter l'Order Placer Number.
+  - un CR d’imagerie pour porter le studyInstanceUID.
+ Fourni si connu pour :
+  - une prescription pour porter l'identifiant EPU de la prescription.</t>
   </si>
   <si>
     <t>Evenement.codeEvenement</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Code de l’évènement documenté (obligatoire pour une Demande d'actes d'imagerie, un CR d’imagerie, CR d’examen de l’enfant et un document d’expression personnelle du patient/usager).</t>
+    <t>Code de l’évènement documenté.  
+ Obligatoire pour :
+  - une demande d'actes d'imagerie (code LOINC ='55115-0' 'Demande d’actes d’imagerie')
+  - un CR d’imagerie (code LOINC de l'acte d'imagerie),
+  - un CR d’examen de l’enfant (code SNOMED CT ='11429006' 'consultation'),
+  - un document d’expression personnelle du patient/usager (code TRE_A00 'EXP_PATIENT' 'Expression personnelle du patient').</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -293,21 +303,14 @@
     <t>Evenement.codeEvenement.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -373,7 +376,12 @@
     <t>Evenement.codeEvenement.translation</t>
   </si>
   <si>
-    <t>Translation (obligatoire pour un CR d’imagerie et un CR d’examen de l’enfant.</t>
+    <t>Translation. 
+ Obligatoire pour : 
+  - un CR d’imagerie pour indiquer
+   - 1..* la (ou les) modalité(s) d'acquisition,
+   - 1..* la (ou les) région(s) anatomique(s)
+  - un CR d’examen de l’enfant pour indiquer l'examen (jdv-examen-enfant-obligatoire-cisis).</t>
   </si>
   <si>
     <t>Evenement.dateHeureEvenement</t>
@@ -383,43 +391,19 @@
 </t>
   </si>
   <si>
-    <t>Date et heure de l’évènement documenté.</t>
+    <t>Date et heure de début et de fin de l’évènement documenté. 
+  Date de début obligatoire pour l'évènement documenté principal.</t>
   </si>
   <si>
     <t>Evenement.executantEvenement</t>
   </si>
   <si>
-    <t xml:space="preserve">BackboneElement
+    <t xml:space="preserve">Base
 </t>
   </si>
   <si>
-    <t>Exécutant.</t>
-  </si>
-  <si>
-    <t>Evenement.executantEvenement.id</t>
-  </si>
-  <si>
-    <t>Evenement.executantEvenement.extension</t>
-  </si>
-  <si>
-    <t>Evenement.executantEvenement.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
+    <t>Exécutant. 
+  Obligatoire pour l'évènement documenté principal.</t>
   </si>
   <si>
     <t>Evenement.executantEvenement.roleFonctionnel</t>
@@ -439,6 +423,10 @@
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PersonneStructure
 </t>
+  </si>
+  <si>
+    <t>Exécutant. 
+  Le cadre d'exercice est obligatoire pour l'évènement documenté principal.</t>
   </si>
 </sst>
 </file>
@@ -740,43 +728,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ17"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.56640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.56640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.921875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.62109375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="69.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="53.56640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -978,7 +966,7 @@
         <v>76</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>74</v>
@@ -992,10 +980,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1003,7 +991,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
         <v>74</v>
@@ -1018,13 +1006,13 @@
         <v>72</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1075,10 +1063,10 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>74</v>
@@ -1092,10 +1080,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1103,10 +1091,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1175,13 +1163,13 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH4" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1203,10 +1191,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1278,10 +1266,10 @@
         <v>89</v>
       </c>
       <c r="AG5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH5" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
@@ -1299,14 +1287,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1318,17 +1306,15 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M6" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>95</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>72</v>
@@ -1365,22 +1351,22 @@
         <v>72</v>
       </c>
       <c r="AB6" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE6" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC6" t="s" s="2">
+      <c r="AF6" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="AG6" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>74</v>
@@ -1389,15 +1375,15 @@
         <v>72</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1405,7 +1391,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>74</v>
@@ -1417,22 +1403,22 @@
         <v>72</v>
       </c>
       <c r="J7" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="K7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="O7" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>72</v>
@@ -1481,10 +1467,10 @@
         <v>72</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>74</v>
@@ -1498,10 +1484,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1509,11 +1495,11 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H8" t="s" s="2">
         <v>72</v>
       </c>
@@ -1521,22 +1507,22 @@
         <v>72</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K8" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="O8" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>72</v>
@@ -1585,13 +1571,13 @@
         <v>72</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH8" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>72</v>
@@ -1602,10 +1588,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1613,7 +1599,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>74</v>
@@ -1631,10 +1617,10 @@
         <v>82</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1685,10 +1671,10 @@
         <v>72</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>74</v>
@@ -1702,10 +1688,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1713,11 +1699,11 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G10" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H10" t="s" s="2">
         <v>72</v>
       </c>
@@ -1728,13 +1714,13 @@
         <v>72</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1785,13 +1771,13 @@
         <v>72</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH10" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH10" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>72</v>
@@ -1802,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1813,10 +1799,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>72</v>
@@ -1828,13 +1814,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1885,27 +1871,27 @@
         <v>72</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1913,11 +1899,11 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G12" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H12" t="s" s="2">
         <v>72</v>
       </c>
@@ -1928,13 +1914,13 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1985,13 +1971,13 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="AG12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH12" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>72</v>
@@ -2002,22 +1988,22 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="G13" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="H13" t="s" s="2">
         <v>72</v>
       </c>
@@ -2028,17 +2014,15 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>72</v>
@@ -2075,31 +2059,31 @@
         <v>72</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
         <v>73</v>
       </c>
-      <c r="AH13" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="AI13" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -2111,39 +2095,35 @@
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>127</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>129</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>72</v>
       </c>
@@ -2191,318 +2171,18 @@
         <v>72</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K17" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
